--- a/02_Шаблоны_и_Форматки/Справочники/Нормативы_производства.xlsx
+++ b/02_Шаблоны_и_Форматки/Справочники/Нормативы_производства.xlsx
@@ -587,11 +587,11 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Ширина реза</t>
+          <t>Ширина реза лазерного трубореза</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Из заявки 85_Т; для лазера уточнить у технолога</t>
+          <t>Предварительно 15.09.2026, уточняется технологом</t>
         </is>
       </c>
     </row>

--- a/02_Шаблоны_и_Форматки/Справочники/Нормативы_производства.xlsx
+++ b/02_Шаблоны_и_Форматки/Справочники/Нормативы_производства.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Предварительно 15.09.2026, уточняется технологом</t>
+          <t>Предварительно 15.09.2026, уточняет начальник КТО</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Справочник читают кнопки вкладки ЕСКД при каждом запуске — после правки и сохранения значения действуют сразу.</t>
+          <t>Справочник правит только начальник КТО; у конструкторов на папку право чтения. Кнопки вкладки ЕСКД читают его при каждом запуске — после правки и сохранения значения действуют сразу у всех.</t>
         </is>
       </c>
     </row>

--- a/02_Шаблоны_и_Форматки/Справочники/Нормативы_производства.xlsx
+++ b/02_Шаблоны_и_Форматки/Справочники/Нормативы_производства.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="Нормативы" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Операции" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Единицы ОКЕИ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Коды 1С" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Справка" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Цвета RAL" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Единицы ОКЕИ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Коды 1С" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Справка" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -973,6 +974,318 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RAL</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Поверхности</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Код 1С краски</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>RAL 9003</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Сигнальный белый</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>глянец, матовый, шагрень, муар</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>RAL 9010</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Чистый белый</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>глянец, матовый, шагрень, муар</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>RAL 9016</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Транспортный белый</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>глянец, матовый, шагрень, муар</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>RAL 9005</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Глубокий чёрный</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>глянец, матовый, шагрень, муар</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>RAL 7035</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Светло-серый</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>глянец, матовый, шагрень, муар</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>RAL 7024</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Графитовый серый</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>глянец, матовый, шагрень, муар</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>RAL 7040</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Серое окно</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>глянец, матовый, шагрень, муар</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>RAL 5005</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Сигнальный синий</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>глянец, матовый, шагрень, муар</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>RAL 5015</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Небесно-синий</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>глянец, матовый, шагрень, муар</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>RAL 3020</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Транспортный красный</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>глянец, матовый, шагрень, муар</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>RAL 1023</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Транспортный жёлтый</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>глянец, матовый, шагрень, муар</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>RAL 6005</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Зелёный мох</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>глянец, матовый, шагрень, муар</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>RAL 6018</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Жёлто-зелёный</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>глянец, матовый, шагрень, муар</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>RAL 2004</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Чистый оранжевый</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>глянец, матовый, шагрень, муар</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>RAL 8017</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Шоколадно-коричневый</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>глянец, матовый, шагрень, муар</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1163,7 +1476,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1205,13 +1518,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1241,12 +1554,19 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>«Единицы ОКЕИ»: единицы измерения по ОК 015-94 для СЗ на производство и списания.</t>
+          <t>«Цвета RAL»: выпадающий список цветов в окне «Цвета покраски»; добавляйте строки с нужными цветами, код 1С краски — для строки краски в комплектации.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>«Единицы ОКЕИ»: единицы измерения по ОК 015-94 для СЗ на производство и списания.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>«Коды 1С»: заполняется позже; кнопка ищет код по номенклатуре или обозначению.</t>
         </is>

--- a/02_Шаблоны_и_Форматки/Справочники/Нормативы_производства.xlsx
+++ b/02_Шаблоны_и_Форматки/Справочники/Нормативы_производства.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Захват трубореза — эта часть хлыста не режется. Вопрос В-2: в сводной 85_Т — 600 мм, ждёт решения владельца</t>
+          <t>Захват трубореза — эта часть хлыста не режется (решение владельца 19.09.2026, В-2)</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,6 @@
       <c r="B8" s="2" t="n">
         <v>1.15</v>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>Коэффициент отхода листового раскроя</t>

--- a/02_Шаблоны_и_Форматки/Справочники/Нормативы_производства.xlsx
+++ b/02_Шаблоны_и_Форматки/Справочники/Нормативы_производства.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Торцовка — на каждый торец хлыста</t>
+          <t>Торцовка — один конец хлыста; второй конец уходит в захват</t>
         </is>
       </c>
     </row>
